--- a/raw-data/assumptions/ofc_and_dep_assumptions.xlsx
+++ b/raw-data/assumptions/ofc_and_dep_assumptions.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgodar\Dropbox\FGZ2023OffshoreWealth\replication\update-to-2023\raw-data\assumptions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34CEC08-4B47-4BAB-8E6B-9E0ED7303FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B161E02-6F66-448A-84DE-1084A8402AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{19DC7AB1-44E4-4D40-A469-C0A475331B64}"/>
+    <workbookView xWindow="31830" yWindow="1425" windowWidth="19230" windowHeight="10095" firstSheet="1" activeTab="1" xr2:uid="{19DC7AB1-44E4-4D40-A469-C0A475331B64}"/>
   </bookViews>
   <sheets>
     <sheet name="ofc_list" sheetId="2" r:id="rId1"/>
-    <sheet name="sharehouseholddep" sheetId="3" r:id="rId2"/>
+    <sheet name="sharehouseholddep_baseline" sheetId="3" r:id="rId2"/>
+    <sheet name="sharehouseholddep_allone" sheetId="4" r:id="rId3"/>
+    <sheet name="sharehouseholddep_freeze" sheetId="5" r:id="rId4"/>
+    <sheet name="sharehouseholddep_hk_low" sheetId="6" r:id="rId5"/>
+    <sheet name="sharehouseholddep_hk_high" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ofc_list!$A$2:$H$2</definedName>
@@ -74,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="218">
   <si>
     <t>FGMZ lists</t>
   </si>
@@ -5123,4 +5127,8494 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA4CC1C-7BB4-4DC8-B554-52EE32C6AFE3}">
+  <dimension ref="A1:Y40"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V1" t="s">
+        <v>169</v>
+      </c>
+      <c r="W1" t="s">
+        <v>193</v>
+      </c>
+      <c r="X1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2001</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2002</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2003</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2004</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2005</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2006</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2007</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2008</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2009</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2010</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2011</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2012</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2013</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2014</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2015</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2017</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2018</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2019</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2022</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+    </row>
+    <row r="28" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+    </row>
+    <row r="29" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+    </row>
+    <row r="30" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+    </row>
+    <row r="31" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+    </row>
+    <row r="32" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+    </row>
+    <row r="33" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+    </row>
+    <row r="34" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+    </row>
+    <row r="35" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+    </row>
+    <row r="36" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15"/>
+    </row>
+    <row r="37" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+    </row>
+    <row r="38" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="Y38" s="15"/>
+    </row>
+    <row r="39" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+    </row>
+    <row r="40" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD1C569-06FD-48C7-AE4A-CE25DDA07E84}">
+  <dimension ref="A1:Y40"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V1" t="s">
+        <v>169</v>
+      </c>
+      <c r="W1" t="s">
+        <v>193</v>
+      </c>
+      <c r="X1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2001</v>
+      </c>
+      <c r="B2">
+        <v>0.7</v>
+      </c>
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2">
+        <v>0.3</v>
+      </c>
+      <c r="E2">
+        <v>0.7</v>
+      </c>
+      <c r="F2">
+        <v>0.7</v>
+      </c>
+      <c r="G2">
+        <v>0.7</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.7</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0.2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0.7</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0.3</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0.7</v>
+      </c>
+      <c r="T2">
+        <v>0.7</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>0.7</v>
+      </c>
+      <c r="W2">
+        <v>0.1</v>
+      </c>
+      <c r="X2" s="12">
+        <v>0.78387258946895599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2002</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
+      </c>
+      <c r="C3">
+        <v>0.3</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <v>0.7</v>
+      </c>
+      <c r="F3">
+        <v>0.7</v>
+      </c>
+      <c r="G3">
+        <v>0.7</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.7</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0.2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.7</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0.3</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0.7</v>
+      </c>
+      <c r="T3">
+        <v>0.7</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>0.7</v>
+      </c>
+      <c r="W3">
+        <v>0.1</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0.78040865063667297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2003</v>
+      </c>
+      <c r="B4">
+        <v>0.7</v>
+      </c>
+      <c r="C4">
+        <v>0.3</v>
+      </c>
+      <c r="D4">
+        <v>0.3</v>
+      </c>
+      <c r="E4">
+        <v>0.7</v>
+      </c>
+      <c r="F4">
+        <v>0.7</v>
+      </c>
+      <c r="G4">
+        <v>0.7</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.7</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0.2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0.7</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0.3</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0.7</v>
+      </c>
+      <c r="T4">
+        <v>0.7</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0.7</v>
+      </c>
+      <c r="W4">
+        <v>0.1</v>
+      </c>
+      <c r="X4" s="12">
+        <v>0.84089493751525879</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2004</v>
+      </c>
+      <c r="B5">
+        <v>0.7</v>
+      </c>
+      <c r="C5">
+        <v>0.3</v>
+      </c>
+      <c r="D5">
+        <v>0.3</v>
+      </c>
+      <c r="E5">
+        <v>0.7</v>
+      </c>
+      <c r="F5">
+        <v>0.7</v>
+      </c>
+      <c r="G5">
+        <v>0.7</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0.2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.7</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0.3</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>0.7</v>
+      </c>
+      <c r="T5">
+        <v>0.7</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>0.7</v>
+      </c>
+      <c r="W5">
+        <v>0.1</v>
+      </c>
+      <c r="X5" s="12">
+        <v>0.83184534311294556</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2005</v>
+      </c>
+      <c r="B6">
+        <v>0.7</v>
+      </c>
+      <c r="C6">
+        <v>0.3</v>
+      </c>
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>0.7</v>
+      </c>
+      <c r="F6">
+        <v>0.7</v>
+      </c>
+      <c r="G6">
+        <v>0.7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.7</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.7</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0.3</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0.7</v>
+      </c>
+      <c r="T6">
+        <v>0.7</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>0.7</v>
+      </c>
+      <c r="W6">
+        <v>0.1</v>
+      </c>
+      <c r="X6" s="12">
+        <v>0.74730253219604492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2006</v>
+      </c>
+      <c r="B7">
+        <v>0.7</v>
+      </c>
+      <c r="C7">
+        <v>0.3</v>
+      </c>
+      <c r="D7">
+        <v>0.3</v>
+      </c>
+      <c r="E7">
+        <v>0.7</v>
+      </c>
+      <c r="F7">
+        <v>0.7</v>
+      </c>
+      <c r="G7">
+        <v>0.7</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.7</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0.3</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0.7</v>
+      </c>
+      <c r="T7">
+        <v>0.7</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>0.7</v>
+      </c>
+      <c r="W7">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="12">
+        <v>0.75868967175483704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2007</v>
+      </c>
+      <c r="B8">
+        <v>0.7</v>
+      </c>
+      <c r="C8">
+        <v>0.3</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="E8">
+        <v>0.7</v>
+      </c>
+      <c r="F8">
+        <v>0.7</v>
+      </c>
+      <c r="G8">
+        <v>0.7</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.7</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0.2</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0.7</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0.3</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0.7</v>
+      </c>
+      <c r="T8">
+        <v>0.7</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0.7</v>
+      </c>
+      <c r="W8">
+        <v>0.1</v>
+      </c>
+      <c r="X8" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2008</v>
+      </c>
+      <c r="B9">
+        <v>0.7</v>
+      </c>
+      <c r="C9">
+        <v>0.3</v>
+      </c>
+      <c r="D9">
+        <v>0.3</v>
+      </c>
+      <c r="E9">
+        <v>0.7</v>
+      </c>
+      <c r="F9">
+        <v>0.7</v>
+      </c>
+      <c r="G9">
+        <v>0.7</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.7</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0.2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0.7</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0.3</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>0.7</v>
+      </c>
+      <c r="T9">
+        <v>0.7</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>0.7</v>
+      </c>
+      <c r="W9">
+        <v>0.1</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2009</v>
+      </c>
+      <c r="B10">
+        <v>0.7</v>
+      </c>
+      <c r="C10">
+        <v>0.3</v>
+      </c>
+      <c r="D10">
+        <v>0.3</v>
+      </c>
+      <c r="E10">
+        <v>0.7</v>
+      </c>
+      <c r="F10">
+        <v>0.7</v>
+      </c>
+      <c r="G10">
+        <v>0.7</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.7</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0.2</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>0.7</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0.3</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>0.7</v>
+      </c>
+      <c r="T10">
+        <v>0.7</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>0.7</v>
+      </c>
+      <c r="W10">
+        <v>0.1</v>
+      </c>
+      <c r="X10" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2010</v>
+      </c>
+      <c r="B11">
+        <v>0.7</v>
+      </c>
+      <c r="C11">
+        <v>0.3</v>
+      </c>
+      <c r="D11">
+        <v>0.3</v>
+      </c>
+      <c r="E11">
+        <v>0.7</v>
+      </c>
+      <c r="F11">
+        <v>0.7</v>
+      </c>
+      <c r="G11">
+        <v>0.7</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.7</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0.2</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0.7</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0.3</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0.7</v>
+      </c>
+      <c r="T11">
+        <v>0.7</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>0.7</v>
+      </c>
+      <c r="W11">
+        <v>0.1</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2011</v>
+      </c>
+      <c r="B12">
+        <v>0.7</v>
+      </c>
+      <c r="C12">
+        <v>0.3</v>
+      </c>
+      <c r="D12">
+        <v>0.3</v>
+      </c>
+      <c r="E12">
+        <v>0.7</v>
+      </c>
+      <c r="F12">
+        <v>0.7</v>
+      </c>
+      <c r="G12">
+        <v>0.7</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.7</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0.2</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>0.7</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0.3</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>0.7</v>
+      </c>
+      <c r="T12">
+        <v>0.7</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>0.7</v>
+      </c>
+      <c r="W12">
+        <v>0.1</v>
+      </c>
+      <c r="X12" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2012</v>
+      </c>
+      <c r="B13">
+        <v>0.7</v>
+      </c>
+      <c r="C13">
+        <v>0.3</v>
+      </c>
+      <c r="D13">
+        <v>0.3</v>
+      </c>
+      <c r="E13">
+        <v>0.7</v>
+      </c>
+      <c r="F13">
+        <v>0.7</v>
+      </c>
+      <c r="G13">
+        <v>0.7</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.7</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0.2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>0.7</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0.3</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>0.7</v>
+      </c>
+      <c r="T13">
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>0.7</v>
+      </c>
+      <c r="W13">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2013</v>
+      </c>
+      <c r="B14">
+        <v>0.7</v>
+      </c>
+      <c r="C14">
+        <v>0.3</v>
+      </c>
+      <c r="D14">
+        <v>0.3</v>
+      </c>
+      <c r="E14">
+        <v>0.7</v>
+      </c>
+      <c r="F14">
+        <v>0.7</v>
+      </c>
+      <c r="G14">
+        <v>0.7</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.7</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0.2</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>0.7</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0.3</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0.7</v>
+      </c>
+      <c r="T14">
+        <v>0.7</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>0.7</v>
+      </c>
+      <c r="W14">
+        <v>0.1</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2014</v>
+      </c>
+      <c r="B15">
+        <v>0.7</v>
+      </c>
+      <c r="C15">
+        <v>0.3</v>
+      </c>
+      <c r="D15">
+        <v>0.3</v>
+      </c>
+      <c r="E15">
+        <v>0.7</v>
+      </c>
+      <c r="F15">
+        <v>0.7</v>
+      </c>
+      <c r="G15">
+        <v>0.7</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.7</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0.2</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0.7</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0.3</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0.7</v>
+      </c>
+      <c r="T15">
+        <v>0.7</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>0.7</v>
+      </c>
+      <c r="W15">
+        <v>0.1</v>
+      </c>
+      <c r="X15" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2015</v>
+      </c>
+      <c r="B16">
+        <v>0.7</v>
+      </c>
+      <c r="C16">
+        <v>0.3</v>
+      </c>
+      <c r="D16">
+        <v>0.3</v>
+      </c>
+      <c r="E16">
+        <v>0.7</v>
+      </c>
+      <c r="F16">
+        <v>0.7</v>
+      </c>
+      <c r="G16">
+        <v>0.7</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.7</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0.2</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0.7</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0.3</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0.7</v>
+      </c>
+      <c r="T16">
+        <v>0.7</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>0.7</v>
+      </c>
+      <c r="W16">
+        <v>0.1</v>
+      </c>
+      <c r="X16" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17">
+        <v>0.7</v>
+      </c>
+      <c r="C17">
+        <v>0.3</v>
+      </c>
+      <c r="D17">
+        <v>0.3</v>
+      </c>
+      <c r="E17">
+        <v>0.7</v>
+      </c>
+      <c r="F17">
+        <v>0.7</v>
+      </c>
+      <c r="G17">
+        <v>0.7</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.7</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0.2</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0.7</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0.3</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>0.7</v>
+      </c>
+      <c r="T17">
+        <v>0.7</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0.7</v>
+      </c>
+      <c r="W17">
+        <v>0.1</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2017</v>
+      </c>
+      <c r="B18">
+        <v>0.7</v>
+      </c>
+      <c r="C18">
+        <v>0.3</v>
+      </c>
+      <c r="D18">
+        <v>0.3</v>
+      </c>
+      <c r="E18">
+        <v>0.7</v>
+      </c>
+      <c r="F18">
+        <v>0.7</v>
+      </c>
+      <c r="G18">
+        <v>0.7</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.7</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0.2</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0.7</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0.3</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>0.7</v>
+      </c>
+      <c r="T18">
+        <v>0.7</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>0.7</v>
+      </c>
+      <c r="W18">
+        <v>0.1</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2018</v>
+      </c>
+      <c r="B19">
+        <v>0.7</v>
+      </c>
+      <c r="C19">
+        <v>0.3</v>
+      </c>
+      <c r="D19">
+        <v>0.3</v>
+      </c>
+      <c r="E19">
+        <v>0.7</v>
+      </c>
+      <c r="F19">
+        <v>0.7</v>
+      </c>
+      <c r="G19">
+        <v>0.7</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.7</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0.2</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0.7</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>0.3</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0.7</v>
+      </c>
+      <c r="T19">
+        <v>0.7</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>0.7</v>
+      </c>
+      <c r="W19">
+        <v>0.1</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2019</v>
+      </c>
+      <c r="B20">
+        <v>0.7</v>
+      </c>
+      <c r="C20">
+        <v>0.3</v>
+      </c>
+      <c r="D20">
+        <v>0.3</v>
+      </c>
+      <c r="E20">
+        <v>0.7</v>
+      </c>
+      <c r="F20">
+        <v>0.7</v>
+      </c>
+      <c r="G20">
+        <v>0.7</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.7</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0.2</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0.7</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0.3</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>0.7</v>
+      </c>
+      <c r="T20">
+        <v>0.7</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>0.7</v>
+      </c>
+      <c r="W20">
+        <v>0.1</v>
+      </c>
+      <c r="X20" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21">
+        <v>0.7</v>
+      </c>
+      <c r="C21">
+        <v>0.3</v>
+      </c>
+      <c r="D21">
+        <v>0.3</v>
+      </c>
+      <c r="E21">
+        <v>0.7</v>
+      </c>
+      <c r="F21">
+        <v>0.7</v>
+      </c>
+      <c r="G21">
+        <v>0.7</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.7</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0.2</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0.7</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0.3</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>0.7</v>
+      </c>
+      <c r="T21">
+        <v>0.7</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>0.7</v>
+      </c>
+      <c r="W21">
+        <v>0.1</v>
+      </c>
+      <c r="X21" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22">
+        <v>0.7</v>
+      </c>
+      <c r="C22">
+        <v>0.3</v>
+      </c>
+      <c r="D22">
+        <v>0.3</v>
+      </c>
+      <c r="E22">
+        <v>0.7</v>
+      </c>
+      <c r="F22">
+        <v>0.7</v>
+      </c>
+      <c r="G22">
+        <v>0.7</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.7</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0.2</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0.7</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>0.3</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>0.7</v>
+      </c>
+      <c r="T22">
+        <v>0.7</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>0.7</v>
+      </c>
+      <c r="W22">
+        <v>0.1</v>
+      </c>
+      <c r="X22" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2022</v>
+      </c>
+      <c r="B23">
+        <v>0.7</v>
+      </c>
+      <c r="C23">
+        <v>0.3</v>
+      </c>
+      <c r="D23">
+        <v>0.3</v>
+      </c>
+      <c r="E23">
+        <v>0.7</v>
+      </c>
+      <c r="F23">
+        <v>0.7</v>
+      </c>
+      <c r="G23">
+        <v>0.7</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.7</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0.2</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0.7</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0.3</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>0.7</v>
+      </c>
+      <c r="T23">
+        <v>0.7</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>0.7</v>
+      </c>
+      <c r="W23">
+        <v>0.1</v>
+      </c>
+      <c r="X23" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24">
+        <v>0.7</v>
+      </c>
+      <c r="C24">
+        <v>0.3</v>
+      </c>
+      <c r="D24">
+        <v>0.3</v>
+      </c>
+      <c r="E24">
+        <v>0.7</v>
+      </c>
+      <c r="F24">
+        <v>0.7</v>
+      </c>
+      <c r="G24">
+        <v>0.7</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.7</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0.2</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0.7</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>0.3</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>0.7</v>
+      </c>
+      <c r="T24">
+        <v>0.7</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>0.7</v>
+      </c>
+      <c r="W24">
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+    </row>
+    <row r="28" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+    </row>
+    <row r="29" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+    </row>
+    <row r="30" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+    </row>
+    <row r="31" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+    </row>
+    <row r="32" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+    </row>
+    <row r="33" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+    </row>
+    <row r="34" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+    </row>
+    <row r="35" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+    </row>
+    <row r="36" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15"/>
+    </row>
+    <row r="37" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+    </row>
+    <row r="38" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="Y38" s="15"/>
+    </row>
+    <row r="39" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+    </row>
+    <row r="40" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3902CEF-DC5D-4600-9164-09ADA25C6898}">
+  <dimension ref="A1:Y40"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V1" t="s">
+        <v>169</v>
+      </c>
+      <c r="W1" t="s">
+        <v>193</v>
+      </c>
+      <c r="X1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2001</v>
+      </c>
+      <c r="B2">
+        <v>0.7</v>
+      </c>
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2">
+        <v>0.3</v>
+      </c>
+      <c r="E2">
+        <v>0.7</v>
+      </c>
+      <c r="F2">
+        <v>0.7</v>
+      </c>
+      <c r="G2">
+        <v>0.7</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.7</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0.2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0.6</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0.3</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0.7</v>
+      </c>
+      <c r="T2">
+        <v>0.7</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>0.7</v>
+      </c>
+      <c r="W2">
+        <v>0.1</v>
+      </c>
+      <c r="X2" s="12">
+        <v>0.78387258946895599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2002</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
+      </c>
+      <c r="C3">
+        <v>0.3</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <v>0.7</v>
+      </c>
+      <c r="F3">
+        <v>0.7</v>
+      </c>
+      <c r="G3">
+        <v>0.7</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.7</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0.2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.6</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0.3</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0.7</v>
+      </c>
+      <c r="T3">
+        <v>0.7</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>0.7</v>
+      </c>
+      <c r="W3">
+        <v>0.1</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0.78040865063667297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2003</v>
+      </c>
+      <c r="B4">
+        <v>0.7</v>
+      </c>
+      <c r="C4">
+        <v>0.3</v>
+      </c>
+      <c r="D4">
+        <v>0.3</v>
+      </c>
+      <c r="E4">
+        <v>0.7</v>
+      </c>
+      <c r="F4">
+        <v>0.7</v>
+      </c>
+      <c r="G4">
+        <v>0.7</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.7</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0.2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0.6</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0.3</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0.7</v>
+      </c>
+      <c r="T4">
+        <v>0.7</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0.7</v>
+      </c>
+      <c r="W4">
+        <v>0.1</v>
+      </c>
+      <c r="X4" s="12">
+        <v>0.84089493751525879</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2004</v>
+      </c>
+      <c r="B5">
+        <v>0.7</v>
+      </c>
+      <c r="C5">
+        <v>0.3</v>
+      </c>
+      <c r="D5">
+        <v>0.3</v>
+      </c>
+      <c r="E5">
+        <v>0.7</v>
+      </c>
+      <c r="F5">
+        <v>0.7</v>
+      </c>
+      <c r="G5">
+        <v>0.7</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0.2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.6</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0.3</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>0.7</v>
+      </c>
+      <c r="T5">
+        <v>0.7</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>0.7</v>
+      </c>
+      <c r="W5">
+        <v>0.1</v>
+      </c>
+      <c r="X5" s="12">
+        <v>0.83184534311294556</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2005</v>
+      </c>
+      <c r="B6">
+        <v>0.7</v>
+      </c>
+      <c r="C6">
+        <v>0.3</v>
+      </c>
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>0.7</v>
+      </c>
+      <c r="F6">
+        <v>0.7</v>
+      </c>
+      <c r="G6">
+        <v>0.7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.7</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.6</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0.3</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0.7</v>
+      </c>
+      <c r="T6">
+        <v>0.7</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>0.7</v>
+      </c>
+      <c r="W6">
+        <v>0.1</v>
+      </c>
+      <c r="X6" s="12">
+        <v>0.74730253219604492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2006</v>
+      </c>
+      <c r="B7">
+        <v>0.7</v>
+      </c>
+      <c r="C7">
+        <v>0.3</v>
+      </c>
+      <c r="D7">
+        <v>0.3</v>
+      </c>
+      <c r="E7">
+        <v>0.7</v>
+      </c>
+      <c r="F7">
+        <v>0.7</v>
+      </c>
+      <c r="G7">
+        <v>0.7</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.6</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0.3</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0.7</v>
+      </c>
+      <c r="T7">
+        <v>0.7</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>0.7</v>
+      </c>
+      <c r="W7">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="12">
+        <v>0.75868967175483704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2007</v>
+      </c>
+      <c r="B8">
+        <v>0.7</v>
+      </c>
+      <c r="C8">
+        <v>0.3</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="E8">
+        <v>0.7</v>
+      </c>
+      <c r="F8">
+        <v>0.7</v>
+      </c>
+      <c r="G8">
+        <v>0.7</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.7</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0.2</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0.6</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0.3</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0.7</v>
+      </c>
+      <c r="T8">
+        <v>0.7</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0.7</v>
+      </c>
+      <c r="W8">
+        <v>0.1</v>
+      </c>
+      <c r="X8" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2008</v>
+      </c>
+      <c r="B9">
+        <v>0.7</v>
+      </c>
+      <c r="C9">
+        <v>0.2</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>0.7</v>
+      </c>
+      <c r="F9">
+        <v>0.7</v>
+      </c>
+      <c r="G9">
+        <v>0.7</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.7</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0.2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0.6</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0.3</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>0.7</v>
+      </c>
+      <c r="T9">
+        <v>0.7</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>0.7</v>
+      </c>
+      <c r="W9">
+        <v>0.1</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0.7344992458820343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2009</v>
+      </c>
+      <c r="B10">
+        <v>0.7</v>
+      </c>
+      <c r="C10">
+        <v>0.15</v>
+      </c>
+      <c r="D10">
+        <v>0.15</v>
+      </c>
+      <c r="E10">
+        <v>0.7</v>
+      </c>
+      <c r="F10">
+        <v>0.7</v>
+      </c>
+      <c r="G10">
+        <v>0.7</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.7</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0.2</v>
+      </c>
+      <c r="M10">
+        <v>0.95</v>
+      </c>
+      <c r="N10">
+        <v>0.6</v>
+      </c>
+      <c r="O10">
+        <v>0.95</v>
+      </c>
+      <c r="P10">
+        <v>0.95</v>
+      </c>
+      <c r="Q10">
+        <v>0.3</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>0.7</v>
+      </c>
+      <c r="T10">
+        <v>0.7</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>0.7</v>
+      </c>
+      <c r="W10">
+        <v>0.1</v>
+      </c>
+      <c r="X10" s="12">
+        <v>0.49356585741043091</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2010</v>
+      </c>
+      <c r="B11">
+        <v>0.7</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>0.7</v>
+      </c>
+      <c r="F11">
+        <v>0.7</v>
+      </c>
+      <c r="G11">
+        <v>0.7</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.7</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0.2</v>
+      </c>
+      <c r="M11">
+        <v>0.9</v>
+      </c>
+      <c r="N11">
+        <v>0.6</v>
+      </c>
+      <c r="O11">
+        <v>0.9</v>
+      </c>
+      <c r="P11">
+        <v>0.9</v>
+      </c>
+      <c r="Q11">
+        <v>0.3</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0.7</v>
+      </c>
+      <c r="T11">
+        <v>0.7</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>0.7</v>
+      </c>
+      <c r="W11">
+        <v>0.1</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0.54089219868183136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2011</v>
+      </c>
+      <c r="B12">
+        <v>0.7</v>
+      </c>
+      <c r="C12">
+        <v>0.05</v>
+      </c>
+      <c r="D12">
+        <v>0.05</v>
+      </c>
+      <c r="E12">
+        <v>0.7</v>
+      </c>
+      <c r="F12">
+        <v>0.7</v>
+      </c>
+      <c r="G12">
+        <v>0.7</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.7</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0.2</v>
+      </c>
+      <c r="M12">
+        <v>0.85</v>
+      </c>
+      <c r="N12">
+        <v>0.6</v>
+      </c>
+      <c r="O12">
+        <v>0.85</v>
+      </c>
+      <c r="P12">
+        <v>0.85</v>
+      </c>
+      <c r="Q12">
+        <v>0.3</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>0.7</v>
+      </c>
+      <c r="T12">
+        <v>0.7</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>0.7</v>
+      </c>
+      <c r="W12">
+        <v>0.1</v>
+      </c>
+      <c r="X12" s="12">
+        <v>0.60131469368934631</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2012</v>
+      </c>
+      <c r="B13">
+        <v>0.7</v>
+      </c>
+      <c r="C13">
+        <v>0.05</v>
+      </c>
+      <c r="D13">
+        <v>0.05</v>
+      </c>
+      <c r="E13">
+        <v>0.7</v>
+      </c>
+      <c r="F13">
+        <v>0.7</v>
+      </c>
+      <c r="G13">
+        <v>0.7</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.7</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0.2</v>
+      </c>
+      <c r="M13">
+        <v>0.8</v>
+      </c>
+      <c r="N13">
+        <v>0.6</v>
+      </c>
+      <c r="O13">
+        <v>0.8</v>
+      </c>
+      <c r="P13">
+        <v>0.8</v>
+      </c>
+      <c r="Q13">
+        <v>0.3</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>0.7</v>
+      </c>
+      <c r="T13">
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>0.7</v>
+      </c>
+      <c r="W13">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="12">
+        <v>0.5737786591053009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2013</v>
+      </c>
+      <c r="B14">
+        <v>0.7</v>
+      </c>
+      <c r="C14">
+        <v>0.05</v>
+      </c>
+      <c r="D14">
+        <v>0.05</v>
+      </c>
+      <c r="E14">
+        <v>0.7</v>
+      </c>
+      <c r="F14">
+        <v>0.7</v>
+      </c>
+      <c r="G14">
+        <v>0.7</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.7</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0.2</v>
+      </c>
+      <c r="M14">
+        <v>0.75</v>
+      </c>
+      <c r="N14">
+        <v>0.6</v>
+      </c>
+      <c r="O14">
+        <v>0.75</v>
+      </c>
+      <c r="P14">
+        <v>0.75</v>
+      </c>
+      <c r="Q14">
+        <v>0.3</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0.7</v>
+      </c>
+      <c r="T14">
+        <v>0.7</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>0.7</v>
+      </c>
+      <c r="W14">
+        <v>0.1</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0.64158472418785095</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2014</v>
+      </c>
+      <c r="B15">
+        <v>0.7</v>
+      </c>
+      <c r="C15">
+        <v>0.05</v>
+      </c>
+      <c r="D15">
+        <v>0.05</v>
+      </c>
+      <c r="E15">
+        <v>0.7</v>
+      </c>
+      <c r="F15">
+        <v>0.7</v>
+      </c>
+      <c r="G15">
+        <v>0.7</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.7</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0.2</v>
+      </c>
+      <c r="M15">
+        <v>0.7</v>
+      </c>
+      <c r="N15">
+        <v>0.6</v>
+      </c>
+      <c r="O15">
+        <v>0.7</v>
+      </c>
+      <c r="P15">
+        <v>0.7</v>
+      </c>
+      <c r="Q15">
+        <v>0.3</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0.7</v>
+      </c>
+      <c r="T15">
+        <v>0.7</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>0.7</v>
+      </c>
+      <c r="W15">
+        <v>0.1</v>
+      </c>
+      <c r="X15" s="12">
+        <v>0.61322280764579773</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2015</v>
+      </c>
+      <c r="B16">
+        <v>0.7</v>
+      </c>
+      <c r="C16" s="13">
+        <f>C15-$C$15/4</f>
+        <v>3.7500000000000006E-2</v>
+      </c>
+      <c r="D16" s="13">
+        <f>D15-$D$15/3</f>
+        <v>3.333333333333334E-2</v>
+      </c>
+      <c r="E16">
+        <v>0.7</v>
+      </c>
+      <c r="F16">
+        <v>0.7</v>
+      </c>
+      <c r="G16">
+        <v>0.7</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.7</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0.2</v>
+      </c>
+      <c r="M16">
+        <v>0.65</v>
+      </c>
+      <c r="N16">
+        <v>0.6</v>
+      </c>
+      <c r="O16">
+        <v>0.65</v>
+      </c>
+      <c r="P16">
+        <v>0.65</v>
+      </c>
+      <c r="Q16">
+        <v>0.3</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0.7</v>
+      </c>
+      <c r="T16">
+        <v>0.7</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>0.7</v>
+      </c>
+      <c r="W16">
+        <v>0.1</v>
+      </c>
+      <c r="X16" s="12">
+        <v>0.58486109972000122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17">
+        <v>0.7</v>
+      </c>
+      <c r="C17" s="13">
+        <f t="shared" ref="C17:C19" si="0">C16-$C$15/4</f>
+        <v>2.5000000000000005E-2</v>
+      </c>
+      <c r="D17" s="13">
+        <f t="shared" ref="D17:D18" si="1">D16-$D$15/4</f>
+        <v>2.0833333333333339E-2</v>
+      </c>
+      <c r="E17">
+        <v>0.7</v>
+      </c>
+      <c r="F17">
+        <v>0.7</v>
+      </c>
+      <c r="G17">
+        <v>0.7</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.7</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0.2</v>
+      </c>
+      <c r="M17">
+        <v>0.65</v>
+      </c>
+      <c r="N17">
+        <v>0.6</v>
+      </c>
+      <c r="O17">
+        <v>0.65</v>
+      </c>
+      <c r="P17">
+        <v>0.65</v>
+      </c>
+      <c r="Q17">
+        <v>0.3</v>
+      </c>
+      <c r="R17">
+        <v>0.9</v>
+      </c>
+      <c r="S17">
+        <v>0.5</v>
+      </c>
+      <c r="T17">
+        <v>0.5</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0.7</v>
+      </c>
+      <c r="W17">
+        <v>0.1</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0.58495855331420898</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2017</v>
+      </c>
+      <c r="B18">
+        <v>0.7</v>
+      </c>
+      <c r="C18" s="13">
+        <f t="shared" si="0"/>
+        <v>1.2500000000000004E-2</v>
+      </c>
+      <c r="D18" s="13">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333384E-3</v>
+      </c>
+      <c r="E18">
+        <v>0.7</v>
+      </c>
+      <c r="F18">
+        <v>0.7</v>
+      </c>
+      <c r="G18">
+        <v>0.7</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.7</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0.2</v>
+      </c>
+      <c r="M18">
+        <v>0.65</v>
+      </c>
+      <c r="N18">
+        <v>0.6</v>
+      </c>
+      <c r="O18">
+        <v>0.65</v>
+      </c>
+      <c r="P18">
+        <v>0.65</v>
+      </c>
+      <c r="Q18">
+        <v>0.3</v>
+      </c>
+      <c r="R18">
+        <v>0.8</v>
+      </c>
+      <c r="S18">
+        <v>0.5</v>
+      </c>
+      <c r="T18">
+        <v>0.5</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>0.7</v>
+      </c>
+      <c r="W18">
+        <v>0.1</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0.5989607572555542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2018</v>
+      </c>
+      <c r="B19">
+        <v>0.7</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0.7</v>
+      </c>
+      <c r="F19">
+        <v>0.7</v>
+      </c>
+      <c r="G19">
+        <v>0.7</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.7</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0.2</v>
+      </c>
+      <c r="M19">
+        <v>0.65</v>
+      </c>
+      <c r="N19">
+        <v>0.6</v>
+      </c>
+      <c r="O19">
+        <v>0.65</v>
+      </c>
+      <c r="P19">
+        <v>0.65</v>
+      </c>
+      <c r="Q19">
+        <v>0.3</v>
+      </c>
+      <c r="R19">
+        <v>0.7</v>
+      </c>
+      <c r="S19">
+        <v>0.5</v>
+      </c>
+      <c r="T19">
+        <v>0.5</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>0.7</v>
+      </c>
+      <c r="W19">
+        <v>0.1</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0.55207974463701248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2019</v>
+      </c>
+      <c r="B20">
+        <v>0.7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0.7</v>
+      </c>
+      <c r="F20">
+        <v>0.7</v>
+      </c>
+      <c r="G20">
+        <v>0.7</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.7</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0.2</v>
+      </c>
+      <c r="M20">
+        <v>0.65</v>
+      </c>
+      <c r="N20">
+        <v>0.6</v>
+      </c>
+      <c r="O20">
+        <v>0.65</v>
+      </c>
+      <c r="P20">
+        <v>0.65</v>
+      </c>
+      <c r="Q20">
+        <v>0.3</v>
+      </c>
+      <c r="R20">
+        <v>0.6</v>
+      </c>
+      <c r="S20">
+        <v>0.5</v>
+      </c>
+      <c r="T20">
+        <v>0.5</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>0.7</v>
+      </c>
+      <c r="W20">
+        <v>0.1</v>
+      </c>
+      <c r="X20" s="12">
+        <v>0.5096895769238472</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21">
+        <v>0.7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0.7</v>
+      </c>
+      <c r="F21">
+        <v>0.7</v>
+      </c>
+      <c r="G21">
+        <v>0.7</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.7</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0.2</v>
+      </c>
+      <c r="M21">
+        <v>0.65</v>
+      </c>
+      <c r="N21">
+        <v>0.6</v>
+      </c>
+      <c r="O21">
+        <v>0.65</v>
+      </c>
+      <c r="P21">
+        <v>0.65</v>
+      </c>
+      <c r="Q21">
+        <v>0.3</v>
+      </c>
+      <c r="R21">
+        <v>0.5</v>
+      </c>
+      <c r="S21">
+        <v>0.5</v>
+      </c>
+      <c r="T21">
+        <v>0.5</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>0.7</v>
+      </c>
+      <c r="W21">
+        <v>0.1</v>
+      </c>
+      <c r="X21" s="12">
+        <v>0.47842603176832199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22">
+        <v>0.7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0.7</v>
+      </c>
+      <c r="F22">
+        <v>0.7</v>
+      </c>
+      <c r="G22">
+        <v>0.7</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.7</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0.2</v>
+      </c>
+      <c r="M22">
+        <v>0.65</v>
+      </c>
+      <c r="N22">
+        <v>0.6</v>
+      </c>
+      <c r="O22">
+        <v>0.65</v>
+      </c>
+      <c r="P22">
+        <v>0.65</v>
+      </c>
+      <c r="Q22">
+        <v>0.3</v>
+      </c>
+      <c r="R22">
+        <v>0.4</v>
+      </c>
+      <c r="S22">
+        <v>0.5</v>
+      </c>
+      <c r="T22">
+        <v>0.5</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>0.7</v>
+      </c>
+      <c r="W22">
+        <v>0.1</v>
+      </c>
+      <c r="X22" s="12">
+        <v>0.46941046416759491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2022</v>
+      </c>
+      <c r="B23">
+        <v>0.7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0.7</v>
+      </c>
+      <c r="F23">
+        <v>0.7</v>
+      </c>
+      <c r="G23">
+        <v>0.7</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.7</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0.2</v>
+      </c>
+      <c r="M23">
+        <v>0.65</v>
+      </c>
+      <c r="N23">
+        <v>0.6</v>
+      </c>
+      <c r="O23">
+        <v>0.65</v>
+      </c>
+      <c r="P23">
+        <v>0.65</v>
+      </c>
+      <c r="Q23">
+        <v>0.3</v>
+      </c>
+      <c r="R23">
+        <v>0.4</v>
+      </c>
+      <c r="S23">
+        <v>0.5</v>
+      </c>
+      <c r="T23">
+        <v>0.5</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>0.7</v>
+      </c>
+      <c r="W23">
+        <v>0.1</v>
+      </c>
+      <c r="X23" s="12">
+        <v>0.64261986315250397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24">
+        <v>0.7</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0.7</v>
+      </c>
+      <c r="F24">
+        <v>0.7</v>
+      </c>
+      <c r="G24">
+        <v>0.7</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.7</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0.2</v>
+      </c>
+      <c r="M24">
+        <v>0.65</v>
+      </c>
+      <c r="N24">
+        <v>0.6</v>
+      </c>
+      <c r="O24">
+        <v>0.65</v>
+      </c>
+      <c r="P24">
+        <v>0.65</v>
+      </c>
+      <c r="Q24">
+        <v>0.3</v>
+      </c>
+      <c r="R24">
+        <v>0.4</v>
+      </c>
+      <c r="S24">
+        <v>0.5</v>
+      </c>
+      <c r="T24">
+        <v>0.5</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>0.7</v>
+      </c>
+      <c r="W24">
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="12">
+        <v>0.73916962742805481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+    </row>
+    <row r="28" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+    </row>
+    <row r="29" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+    </row>
+    <row r="30" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+    </row>
+    <row r="31" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+    </row>
+    <row r="32" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+    </row>
+    <row r="33" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+    </row>
+    <row r="34" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+    </row>
+    <row r="35" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+    </row>
+    <row r="36" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15"/>
+    </row>
+    <row r="37" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+    </row>
+    <row r="38" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="Y38" s="15"/>
+    </row>
+    <row r="39" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+    </row>
+    <row r="40" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B08D87-1150-4F77-9C13-AF5586439AA9}">
+  <dimension ref="A1:Y40"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V1" t="s">
+        <v>169</v>
+      </c>
+      <c r="W1" t="s">
+        <v>193</v>
+      </c>
+      <c r="X1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2001</v>
+      </c>
+      <c r="B2">
+        <v>0.7</v>
+      </c>
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2">
+        <v>0.3</v>
+      </c>
+      <c r="E2">
+        <v>0.7</v>
+      </c>
+      <c r="F2">
+        <v>0.7</v>
+      </c>
+      <c r="G2">
+        <v>0.7</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.7</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0.2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0.8</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0.3</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0.7</v>
+      </c>
+      <c r="T2">
+        <v>0.7</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>0.7</v>
+      </c>
+      <c r="W2">
+        <v>0.1</v>
+      </c>
+      <c r="X2" s="12">
+        <v>0.78387258946895599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2002</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
+      </c>
+      <c r="C3">
+        <v>0.3</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <v>0.7</v>
+      </c>
+      <c r="F3">
+        <v>0.7</v>
+      </c>
+      <c r="G3">
+        <v>0.7</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.7</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0.2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.8</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0.3</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0.7</v>
+      </c>
+      <c r="T3">
+        <v>0.7</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>0.7</v>
+      </c>
+      <c r="W3">
+        <v>0.1</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0.78040865063667297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2003</v>
+      </c>
+      <c r="B4">
+        <v>0.7</v>
+      </c>
+      <c r="C4">
+        <v>0.3</v>
+      </c>
+      <c r="D4">
+        <v>0.3</v>
+      </c>
+      <c r="E4">
+        <v>0.7</v>
+      </c>
+      <c r="F4">
+        <v>0.7</v>
+      </c>
+      <c r="G4">
+        <v>0.7</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.7</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0.2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0.8</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0.3</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0.7</v>
+      </c>
+      <c r="T4">
+        <v>0.7</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0.7</v>
+      </c>
+      <c r="W4">
+        <v>0.1</v>
+      </c>
+      <c r="X4" s="12">
+        <v>0.84089493751525879</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2004</v>
+      </c>
+      <c r="B5">
+        <v>0.7</v>
+      </c>
+      <c r="C5">
+        <v>0.3</v>
+      </c>
+      <c r="D5">
+        <v>0.3</v>
+      </c>
+      <c r="E5">
+        <v>0.7</v>
+      </c>
+      <c r="F5">
+        <v>0.7</v>
+      </c>
+      <c r="G5">
+        <v>0.7</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0.2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.8</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0.3</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>0.7</v>
+      </c>
+      <c r="T5">
+        <v>0.7</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>0.7</v>
+      </c>
+      <c r="W5">
+        <v>0.1</v>
+      </c>
+      <c r="X5" s="12">
+        <v>0.83184534311294556</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2005</v>
+      </c>
+      <c r="B6">
+        <v>0.7</v>
+      </c>
+      <c r="C6">
+        <v>0.3</v>
+      </c>
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>0.7</v>
+      </c>
+      <c r="F6">
+        <v>0.7</v>
+      </c>
+      <c r="G6">
+        <v>0.7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.7</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.8</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0.3</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0.7</v>
+      </c>
+      <c r="T6">
+        <v>0.7</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>0.7</v>
+      </c>
+      <c r="W6">
+        <v>0.1</v>
+      </c>
+      <c r="X6" s="12">
+        <v>0.74730253219604492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2006</v>
+      </c>
+      <c r="B7">
+        <v>0.7</v>
+      </c>
+      <c r="C7">
+        <v>0.3</v>
+      </c>
+      <c r="D7">
+        <v>0.3</v>
+      </c>
+      <c r="E7">
+        <v>0.7</v>
+      </c>
+      <c r="F7">
+        <v>0.7</v>
+      </c>
+      <c r="G7">
+        <v>0.7</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.8</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0.3</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0.7</v>
+      </c>
+      <c r="T7">
+        <v>0.7</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>0.7</v>
+      </c>
+      <c r="W7">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="12">
+        <v>0.75868967175483704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2007</v>
+      </c>
+      <c r="B8">
+        <v>0.7</v>
+      </c>
+      <c r="C8">
+        <v>0.3</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="E8">
+        <v>0.7</v>
+      </c>
+      <c r="F8">
+        <v>0.7</v>
+      </c>
+      <c r="G8">
+        <v>0.7</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.7</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0.2</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0.8</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0.3</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0.7</v>
+      </c>
+      <c r="T8">
+        <v>0.7</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0.7</v>
+      </c>
+      <c r="W8">
+        <v>0.1</v>
+      </c>
+      <c r="X8" s="12">
+        <v>0.68545055389404297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2008</v>
+      </c>
+      <c r="B9">
+        <v>0.7</v>
+      </c>
+      <c r="C9">
+        <v>0.2</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>0.7</v>
+      </c>
+      <c r="F9">
+        <v>0.7</v>
+      </c>
+      <c r="G9">
+        <v>0.7</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.7</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0.2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0.8</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0.3</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>0.7</v>
+      </c>
+      <c r="T9">
+        <v>0.7</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>0.7</v>
+      </c>
+      <c r="W9">
+        <v>0.1</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0.7344992458820343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2009</v>
+      </c>
+      <c r="B10">
+        <v>0.7</v>
+      </c>
+      <c r="C10">
+        <v>0.15</v>
+      </c>
+      <c r="D10">
+        <v>0.15</v>
+      </c>
+      <c r="E10">
+        <v>0.7</v>
+      </c>
+      <c r="F10">
+        <v>0.7</v>
+      </c>
+      <c r="G10">
+        <v>0.7</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.7</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0.2</v>
+      </c>
+      <c r="M10">
+        <v>0.95</v>
+      </c>
+      <c r="N10">
+        <v>0.8</v>
+      </c>
+      <c r="O10">
+        <v>0.95</v>
+      </c>
+      <c r="P10">
+        <v>0.95</v>
+      </c>
+      <c r="Q10">
+        <v>0.3</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>0.7</v>
+      </c>
+      <c r="T10">
+        <v>0.7</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>0.7</v>
+      </c>
+      <c r="W10">
+        <v>0.1</v>
+      </c>
+      <c r="X10" s="12">
+        <v>0.49356585741043091</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2010</v>
+      </c>
+      <c r="B11">
+        <v>0.7</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>0.7</v>
+      </c>
+      <c r="F11">
+        <v>0.7</v>
+      </c>
+      <c r="G11">
+        <v>0.7</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.7</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0.2</v>
+      </c>
+      <c r="M11">
+        <v>0.9</v>
+      </c>
+      <c r="N11">
+        <v>0.8</v>
+      </c>
+      <c r="O11">
+        <v>0.9</v>
+      </c>
+      <c r="P11">
+        <v>0.9</v>
+      </c>
+      <c r="Q11">
+        <v>0.3</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0.7</v>
+      </c>
+      <c r="T11">
+        <v>0.7</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>0.7</v>
+      </c>
+      <c r="W11">
+        <v>0.1</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0.54089219868183136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2011</v>
+      </c>
+      <c r="B12">
+        <v>0.7</v>
+      </c>
+      <c r="C12">
+        <v>0.05</v>
+      </c>
+      <c r="D12">
+        <v>0.05</v>
+      </c>
+      <c r="E12">
+        <v>0.7</v>
+      </c>
+      <c r="F12">
+        <v>0.7</v>
+      </c>
+      <c r="G12">
+        <v>0.7</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.7</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0.2</v>
+      </c>
+      <c r="M12">
+        <v>0.85</v>
+      </c>
+      <c r="N12">
+        <v>0.8</v>
+      </c>
+      <c r="O12">
+        <v>0.85</v>
+      </c>
+      <c r="P12">
+        <v>0.85</v>
+      </c>
+      <c r="Q12">
+        <v>0.3</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>0.7</v>
+      </c>
+      <c r="T12">
+        <v>0.7</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>0.7</v>
+      </c>
+      <c r="W12">
+        <v>0.1</v>
+      </c>
+      <c r="X12" s="12">
+        <v>0.60131469368934631</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2012</v>
+      </c>
+      <c r="B13">
+        <v>0.7</v>
+      </c>
+      <c r="C13">
+        <v>0.05</v>
+      </c>
+      <c r="D13">
+        <v>0.05</v>
+      </c>
+      <c r="E13">
+        <v>0.7</v>
+      </c>
+      <c r="F13">
+        <v>0.7</v>
+      </c>
+      <c r="G13">
+        <v>0.7</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.7</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0.2</v>
+      </c>
+      <c r="M13">
+        <v>0.8</v>
+      </c>
+      <c r="N13">
+        <v>0.8</v>
+      </c>
+      <c r="O13">
+        <v>0.8</v>
+      </c>
+      <c r="P13">
+        <v>0.8</v>
+      </c>
+      <c r="Q13">
+        <v>0.3</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>0.7</v>
+      </c>
+      <c r="T13">
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>0.7</v>
+      </c>
+      <c r="W13">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="12">
+        <v>0.5737786591053009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2013</v>
+      </c>
+      <c r="B14">
+        <v>0.7</v>
+      </c>
+      <c r="C14">
+        <v>0.05</v>
+      </c>
+      <c r="D14">
+        <v>0.05</v>
+      </c>
+      <c r="E14">
+        <v>0.7</v>
+      </c>
+      <c r="F14">
+        <v>0.7</v>
+      </c>
+      <c r="G14">
+        <v>0.7</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.7</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0.2</v>
+      </c>
+      <c r="M14">
+        <v>0.75</v>
+      </c>
+      <c r="N14">
+        <v>0.8</v>
+      </c>
+      <c r="O14">
+        <v>0.75</v>
+      </c>
+      <c r="P14">
+        <v>0.75</v>
+      </c>
+      <c r="Q14">
+        <v>0.3</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0.7</v>
+      </c>
+      <c r="T14">
+        <v>0.7</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>0.7</v>
+      </c>
+      <c r="W14">
+        <v>0.1</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0.64158472418785095</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2014</v>
+      </c>
+      <c r="B15">
+        <v>0.7</v>
+      </c>
+      <c r="C15">
+        <v>0.05</v>
+      </c>
+      <c r="D15">
+        <v>0.05</v>
+      </c>
+      <c r="E15">
+        <v>0.7</v>
+      </c>
+      <c r="F15">
+        <v>0.7</v>
+      </c>
+      <c r="G15">
+        <v>0.7</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.7</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0.2</v>
+      </c>
+      <c r="M15">
+        <v>0.7</v>
+      </c>
+      <c r="N15">
+        <v>0.8</v>
+      </c>
+      <c r="O15">
+        <v>0.7</v>
+      </c>
+      <c r="P15">
+        <v>0.7</v>
+      </c>
+      <c r="Q15">
+        <v>0.3</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0.7</v>
+      </c>
+      <c r="T15">
+        <v>0.7</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>0.7</v>
+      </c>
+      <c r="W15">
+        <v>0.1</v>
+      </c>
+      <c r="X15" s="12">
+        <v>0.61322280764579773</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2015</v>
+      </c>
+      <c r="B16">
+        <v>0.7</v>
+      </c>
+      <c r="C16" s="13">
+        <f>C15-$C$15/4</f>
+        <v>3.7500000000000006E-2</v>
+      </c>
+      <c r="D16" s="13">
+        <f>D15-$D$15/3</f>
+        <v>3.333333333333334E-2</v>
+      </c>
+      <c r="E16">
+        <v>0.7</v>
+      </c>
+      <c r="F16">
+        <v>0.7</v>
+      </c>
+      <c r="G16">
+        <v>0.7</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.7</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0.2</v>
+      </c>
+      <c r="M16">
+        <v>0.65</v>
+      </c>
+      <c r="N16">
+        <v>0.8</v>
+      </c>
+      <c r="O16">
+        <v>0.65</v>
+      </c>
+      <c r="P16">
+        <v>0.65</v>
+      </c>
+      <c r="Q16">
+        <v>0.3</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0.7</v>
+      </c>
+      <c r="T16">
+        <v>0.7</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>0.7</v>
+      </c>
+      <c r="W16">
+        <v>0.1</v>
+      </c>
+      <c r="X16" s="12">
+        <v>0.58486109972000122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17">
+        <v>0.7</v>
+      </c>
+      <c r="C17" s="13">
+        <f t="shared" ref="C17:C19" si="0">C16-$C$15/4</f>
+        <v>2.5000000000000005E-2</v>
+      </c>
+      <c r="D17" s="13">
+        <f t="shared" ref="D17:D18" si="1">D16-$D$15/4</f>
+        <v>2.0833333333333339E-2</v>
+      </c>
+      <c r="E17">
+        <v>0.7</v>
+      </c>
+      <c r="F17">
+        <v>0.7</v>
+      </c>
+      <c r="G17">
+        <v>0.7</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.7</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0.2</v>
+      </c>
+      <c r="M17">
+        <v>0.65</v>
+      </c>
+      <c r="N17">
+        <v>0.8</v>
+      </c>
+      <c r="O17">
+        <v>0.65</v>
+      </c>
+      <c r="P17">
+        <v>0.65</v>
+      </c>
+      <c r="Q17">
+        <v>0.3</v>
+      </c>
+      <c r="R17">
+        <v>0.9</v>
+      </c>
+      <c r="S17">
+        <v>0.5</v>
+      </c>
+      <c r="T17">
+        <v>0.5</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0.7</v>
+      </c>
+      <c r="W17">
+        <v>0.1</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0.58495855331420898</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2017</v>
+      </c>
+      <c r="B18">
+        <v>0.7</v>
+      </c>
+      <c r="C18" s="13">
+        <f t="shared" si="0"/>
+        <v>1.2500000000000004E-2</v>
+      </c>
+      <c r="D18" s="13">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333384E-3</v>
+      </c>
+      <c r="E18">
+        <v>0.7</v>
+      </c>
+      <c r="F18">
+        <v>0.7</v>
+      </c>
+      <c r="G18">
+        <v>0.7</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.7</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0.2</v>
+      </c>
+      <c r="M18">
+        <v>0.65</v>
+      </c>
+      <c r="N18">
+        <v>0.8</v>
+      </c>
+      <c r="O18">
+        <v>0.65</v>
+      </c>
+      <c r="P18">
+        <v>0.65</v>
+      </c>
+      <c r="Q18">
+        <v>0.3</v>
+      </c>
+      <c r="R18">
+        <v>0.8</v>
+      </c>
+      <c r="S18">
+        <v>0.5</v>
+      </c>
+      <c r="T18">
+        <v>0.5</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>0.7</v>
+      </c>
+      <c r="W18">
+        <v>0.1</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0.5989607572555542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2018</v>
+      </c>
+      <c r="B19">
+        <v>0.7</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0.7</v>
+      </c>
+      <c r="F19">
+        <v>0.7</v>
+      </c>
+      <c r="G19">
+        <v>0.7</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.7</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0.2</v>
+      </c>
+      <c r="M19">
+        <v>0.65</v>
+      </c>
+      <c r="N19">
+        <v>0.8</v>
+      </c>
+      <c r="O19">
+        <v>0.65</v>
+      </c>
+      <c r="P19">
+        <v>0.65</v>
+      </c>
+      <c r="Q19">
+        <v>0.3</v>
+      </c>
+      <c r="R19">
+        <v>0.7</v>
+      </c>
+      <c r="S19">
+        <v>0.5</v>
+      </c>
+      <c r="T19">
+        <v>0.5</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>0.7</v>
+      </c>
+      <c r="W19">
+        <v>0.1</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0.55207974463701248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2019</v>
+      </c>
+      <c r="B20">
+        <v>0.7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0.7</v>
+      </c>
+      <c r="F20">
+        <v>0.7</v>
+      </c>
+      <c r="G20">
+        <v>0.7</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.7</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0.2</v>
+      </c>
+      <c r="M20">
+        <v>0.65</v>
+      </c>
+      <c r="N20">
+        <v>0.8</v>
+      </c>
+      <c r="O20">
+        <v>0.65</v>
+      </c>
+      <c r="P20">
+        <v>0.65</v>
+      </c>
+      <c r="Q20">
+        <v>0.3</v>
+      </c>
+      <c r="R20">
+        <v>0.6</v>
+      </c>
+      <c r="S20">
+        <v>0.5</v>
+      </c>
+      <c r="T20">
+        <v>0.5</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>0.7</v>
+      </c>
+      <c r="W20">
+        <v>0.1</v>
+      </c>
+      <c r="X20" s="12">
+        <v>0.5096895769238472</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21">
+        <v>0.7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0.7</v>
+      </c>
+      <c r="F21">
+        <v>0.7</v>
+      </c>
+      <c r="G21">
+        <v>0.7</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.7</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0.2</v>
+      </c>
+      <c r="M21">
+        <v>0.65</v>
+      </c>
+      <c r="N21">
+        <v>0.8</v>
+      </c>
+      <c r="O21">
+        <v>0.65</v>
+      </c>
+      <c r="P21">
+        <v>0.65</v>
+      </c>
+      <c r="Q21">
+        <v>0.3</v>
+      </c>
+      <c r="R21">
+        <v>0.5</v>
+      </c>
+      <c r="S21">
+        <v>0.5</v>
+      </c>
+      <c r="T21">
+        <v>0.5</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>0.7</v>
+      </c>
+      <c r="W21">
+        <v>0.1</v>
+      </c>
+      <c r="X21" s="12">
+        <v>0.47842603176832199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22">
+        <v>0.7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0.7</v>
+      </c>
+      <c r="F22">
+        <v>0.7</v>
+      </c>
+      <c r="G22">
+        <v>0.7</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.7</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0.2</v>
+      </c>
+      <c r="M22">
+        <v>0.65</v>
+      </c>
+      <c r="N22">
+        <v>0.8</v>
+      </c>
+      <c r="O22">
+        <v>0.65</v>
+      </c>
+      <c r="P22">
+        <v>0.65</v>
+      </c>
+      <c r="Q22">
+        <v>0.3</v>
+      </c>
+      <c r="R22">
+        <v>0.4</v>
+      </c>
+      <c r="S22">
+        <v>0.5</v>
+      </c>
+      <c r="T22">
+        <v>0.5</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>0.7</v>
+      </c>
+      <c r="W22">
+        <v>0.1</v>
+      </c>
+      <c r="X22" s="12">
+        <v>0.46941046416759491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2022</v>
+      </c>
+      <c r="B23">
+        <v>0.7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0.7</v>
+      </c>
+      <c r="F23">
+        <v>0.7</v>
+      </c>
+      <c r="G23">
+        <v>0.7</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.7</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0.2</v>
+      </c>
+      <c r="M23">
+        <v>0.65</v>
+      </c>
+      <c r="N23">
+        <v>0.8</v>
+      </c>
+      <c r="O23">
+        <v>0.65</v>
+      </c>
+      <c r="P23">
+        <v>0.65</v>
+      </c>
+      <c r="Q23">
+        <v>0.3</v>
+      </c>
+      <c r="R23">
+        <v>0.4</v>
+      </c>
+      <c r="S23">
+        <v>0.5</v>
+      </c>
+      <c r="T23">
+        <v>0.5</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>0.7</v>
+      </c>
+      <c r="W23">
+        <v>0.1</v>
+      </c>
+      <c r="X23" s="12">
+        <v>0.64261986315250397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24">
+        <v>0.7</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0.7</v>
+      </c>
+      <c r="F24">
+        <v>0.7</v>
+      </c>
+      <c r="G24">
+        <v>0.7</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.7</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0.2</v>
+      </c>
+      <c r="M24">
+        <v>0.65</v>
+      </c>
+      <c r="N24">
+        <v>0.8</v>
+      </c>
+      <c r="O24">
+        <v>0.65</v>
+      </c>
+      <c r="P24">
+        <v>0.65</v>
+      </c>
+      <c r="Q24">
+        <v>0.3</v>
+      </c>
+      <c r="R24">
+        <v>0.4</v>
+      </c>
+      <c r="S24">
+        <v>0.5</v>
+      </c>
+      <c r="T24">
+        <v>0.5</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>0.7</v>
+      </c>
+      <c r="W24">
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="12">
+        <v>0.73916962742805481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+    </row>
+    <row r="28" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+    </row>
+    <row r="29" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+    </row>
+    <row r="30" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+    </row>
+    <row r="31" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+    </row>
+    <row r="32" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+    </row>
+    <row r="33" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+    </row>
+    <row r="34" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+    </row>
+    <row r="35" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+    </row>
+    <row r="36" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15"/>
+    </row>
+    <row r="37" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+    </row>
+    <row r="38" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="Y38" s="15"/>
+    </row>
+    <row r="39" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+    </row>
+    <row r="40" spans="6:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>